--- a/result/train_info_googlenet_part_detrend_plr_stft_bin_win_pca.xlsx
+++ b/result/train_info_googlenet_part_detrend_plr_stft_bin_win_pca.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,47 +417,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>epoch</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>train_loss</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>lr</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>test_loss</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>test_acc</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>precision</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>recall</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>f1</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>time</t>
         </is>
@@ -480,28 +468,28 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.3646331060937928</v>
+        <v>0.4009350760332011</v>
       </c>
       <c r="C2" t="n">
         <v>0.001</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1527638372651042</v>
+        <v>0.1859495860893698</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9438870308435526</v>
+        <v>0.9221479004087699</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9394717534849596</v>
+        <v>0.8936096718480138</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9492216456634545</v>
+        <v>0.9588584136397331</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9443215339233039</v>
+        <v>0.9250849275880565</v>
       </c>
       <c r="I2" t="n">
-        <v>70.10688829421997</v>
+        <v>41.92679977416992</v>
       </c>
     </row>
     <row r="3">
@@ -509,28 +497,28 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.130936327243686</v>
+        <v>0.1427397723911665</v>
       </c>
       <c r="C3" t="n">
         <v>0.0009997532801828658</v>
       </c>
       <c r="D3" t="n">
-        <v>0.09170166331414993</v>
+        <v>0.1050638566179388</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9665551839464883</v>
+        <v>0.9589371980676329</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9857253086419753</v>
+        <v>0.9561694290976059</v>
       </c>
       <c r="G3" t="n">
-        <v>0.946997776130467</v>
+        <v>0.9621942179392142</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9659735349716446</v>
+        <v>0.9591723628302236</v>
       </c>
       <c r="I3" t="n">
-        <v>71.50082969665527</v>
+        <v>41.64499711990356</v>
       </c>
     </row>
     <row r="4">
@@ -538,28 +526,28 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.06423891029517162</v>
+        <v>0.07078111816383068</v>
       </c>
       <c r="C4" t="n">
         <v>0.0009990133642141358</v>
       </c>
       <c r="D4" t="n">
-        <v>0.05650932556734635</v>
+        <v>0.04653979835414587</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9804905239687849</v>
+        <v>0.9836492010405053</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9757798165137614</v>
+        <v>0.9854910714285714</v>
       </c>
       <c r="G4" t="n">
-        <v>0.985544848035582</v>
+        <v>0.9818383988139362</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9806380232343721</v>
+        <v>0.9836613442257706</v>
       </c>
       <c r="I4" t="n">
-        <v>72.27019548416138</v>
+        <v>42.55778288841248</v>
       </c>
     </row>
     <row r="5">
@@ -567,28 +555,28 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.04794423690551469</v>
+        <v>0.0434276515180847</v>
       </c>
       <c r="C5" t="n">
         <v>0.00099778098230154</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03262676565684709</v>
+        <v>0.06089273477786017</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9895949461166852</v>
+        <v>0.9777034559643255</v>
       </c>
       <c r="F5" t="n">
-        <v>0.986019131714496</v>
+        <v>0.9860482654600302</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9933283914010378</v>
+        <v>0.969236471460341</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9896602658788775</v>
+        <v>0.9775700934579439</v>
       </c>
       <c r="I5" t="n">
-        <v>72.79658770561218</v>
+        <v>42.56042909622192</v>
       </c>
     </row>
     <row r="6">
@@ -596,28 +584,28 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.04123800346981748</v>
+        <v>0.03874743907955609</v>
       </c>
       <c r="C6" t="n">
         <v>0.000996057350657239</v>
       </c>
       <c r="D6" t="n">
-        <v>0.05439515854783092</v>
+        <v>0.03908786186521333</v>
       </c>
       <c r="E6" t="n">
-        <v>0.981419546636938</v>
+        <v>0.9869936826458565</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9814677538917717</v>
+        <v>0.9820249449743214</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9814677538917717</v>
+        <v>0.9922164566345441</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9814677538917717</v>
+        <v>0.987094395280236</v>
       </c>
       <c r="I6" t="n">
-        <v>73.00806021690369</v>
+        <v>42.42534303665161</v>
       </c>
     </row>
     <row r="7">
@@ -625,28 +613,28 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.02885425735355312</v>
+        <v>0.02730249310333356</v>
       </c>
       <c r="C7" t="n">
         <v>0.0009938441702975688</v>
       </c>
       <c r="D7" t="n">
-        <v>0.03821445517923915</v>
+        <v>0.05269550383070307</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9875510962467484</v>
+        <v>0.9810479375696767</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9947348627303497</v>
+        <v>0.9939117199391172</v>
       </c>
       <c r="G7" t="n">
-        <v>0.980355819125278</v>
+        <v>0.9681245366938473</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9874929998133284</v>
+        <v>0.9808486669170109</v>
       </c>
       <c r="I7" t="n">
-        <v>73.54614663124084</v>
+        <v>42.5981912612915</v>
       </c>
     </row>
     <row r="8">
@@ -654,28 +642,28 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.03152800630094805</v>
+        <v>0.02607441311086325</v>
       </c>
       <c r="C8" t="n">
         <v>0.0009911436253643444</v>
       </c>
       <c r="D8" t="n">
-        <v>0.04542836811622197</v>
+        <v>0.05185320925245822</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9849498327759197</v>
+        <v>0.9817911557041992</v>
       </c>
       <c r="F8" t="n">
-        <v>0.994333207404609</v>
+        <v>0.9727272727272728</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9755374351371386</v>
+        <v>0.991475166790215</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9848456501403181</v>
+        <v>0.9820117474302497</v>
       </c>
       <c r="I8" t="n">
-        <v>73.15507984161377</v>
+        <v>42.84124946594238</v>
       </c>
     </row>
     <row r="9">
@@ -683,28 +671,28 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.02159905866836976</v>
+        <v>0.02620080778870249</v>
       </c>
       <c r="C9" t="n">
         <v>0.0009879583809693736</v>
       </c>
       <c r="D9" t="n">
-        <v>0.06160656303599939</v>
+        <v>0.0282857273867183</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9775176514306949</v>
+        <v>0.9912671869193609</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9724972497249725</v>
+        <v>0.9867792875504958</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9829503335804299</v>
+        <v>0.9959229058561898</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9776958525345623</v>
+        <v>0.9913300129127467</v>
       </c>
       <c r="I9" t="n">
-        <v>72.41643333435059</v>
+        <v>42.62973713874817</v>
       </c>
     </row>
     <row r="10">
@@ -712,28 +700,28 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>0.02490828994062714</v>
+        <v>0.01655061890473721</v>
       </c>
       <c r="C10" t="n">
         <v>0.0009842915805643154</v>
       </c>
       <c r="D10" t="n">
-        <v>0.05960373115586668</v>
+        <v>0.03165997556242307</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9823485693050911</v>
+        <v>0.989223337049424</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9913174782936958</v>
+        <v>0.9806991988346686</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9733135656041513</v>
+        <v>0.9981467753891772</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9822330278660931</v>
+        <v>0.9893460690668626</v>
       </c>
       <c r="I10" t="n">
-        <v>73.28274440765381</v>
+        <v>42.93143177032471</v>
       </c>
     </row>
     <row r="11">
@@ -741,28 +729,28 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>0.01743600141483824</v>
+        <v>0.01813480038867053</v>
       </c>
       <c r="C11" t="n">
         <v>0.0009801468428384714</v>
       </c>
       <c r="D11" t="n">
-        <v>0.04983104548996353</v>
+        <v>0.04876948010466425</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9860646599777034</v>
+        <v>0.9849498327759197</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9756982227058397</v>
+        <v>0.9722121977625406</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9970348406226834</v>
+        <v>0.9985174203113417</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9862511457378552</v>
+        <v>0.9851892484914976</v>
       </c>
       <c r="I11" t="n">
-        <v>72.85925531387329</v>
+        <v>42.99341320991516</v>
       </c>
     </row>
     <row r="12">
@@ -770,28 +758,28 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>0.02081038920362937</v>
+        <v>0.01848549871731592</v>
       </c>
       <c r="C12" t="n">
         <v>0.0009755282581475767</v>
       </c>
       <c r="D12" t="n">
-        <v>0.06175775875505501</v>
+        <v>0.03340997192072689</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9825343738387217</v>
+        <v>0.9890375325157934</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.981745162468054</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9962935507783544</v>
+        <v>0.9966641957005189</v>
       </c>
       <c r="H12" t="n">
-        <v>0.9828153564899451</v>
+        <v>0.9891484274416038</v>
       </c>
       <c r="I12" t="n">
-        <v>72.83803081512451</v>
+        <v>42.8511176109314</v>
       </c>
     </row>
     <row r="13">
@@ -799,28 +787,28 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>0.01988081777289117</v>
+        <v>0.01622568996918997</v>
       </c>
       <c r="C13" t="n">
         <v>0.0009704403844771127</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0397119677578066</v>
+        <v>0.01452548046585671</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9890375325157934</v>
+        <v>0.9957264957264957</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9918002236302647</v>
+        <v>0.9962894248608535</v>
       </c>
       <c r="G13" t="n">
-        <v>0.986286137879911</v>
+        <v>0.9951816160118606</v>
       </c>
       <c r="H13" t="n">
-        <v>0.9890354952611039</v>
+        <v>0.9957352123122566</v>
       </c>
       <c r="I13" t="n">
-        <v>73.21877527236938</v>
+        <v>42.93794465065002</v>
       </c>
     </row>
     <row r="14">
@@ -828,28 +816,28 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>0.01951585580465276</v>
+        <v>0.01250348329764762</v>
       </c>
       <c r="C14" t="n">
         <v>0.0009648882429441257</v>
       </c>
       <c r="D14" t="n">
-        <v>0.03720529098425353</v>
+        <v>0.05602919484714307</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9897807506503159</v>
+        <v>0.9881085098476403</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9842433125687065</v>
+        <v>0.9914179104477612</v>
       </c>
       <c r="G14" t="n">
-        <v>0.9955522609340252</v>
+        <v>0.9848035581912528</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9898654873779252</v>
+        <v>0.9880996653030867</v>
       </c>
       <c r="I14" t="n">
-        <v>73.41461873054504</v>
+        <v>43.05993890762329</v>
       </c>
     </row>
     <row r="15">
@@ -857,28 +845,28 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>0.01516352705392823</v>
+        <v>0.0162195960090801</v>
       </c>
       <c r="C15" t="n">
         <v>0.0009588773128419905</v>
       </c>
       <c r="D15" t="n">
-        <v>0.03468826231832572</v>
+        <v>0.03182653468098773</v>
       </c>
       <c r="E15" t="n">
-        <v>0.990709773318469</v>
+        <v>0.9903381642512077</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9977443609022556</v>
+        <v>0.9831994156318481</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9836916234247591</v>
+        <v>0.9977761304670126</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9906681597611049</v>
+        <v>0.9904341427520236</v>
       </c>
       <c r="I15" t="n">
-        <v>74.26113653182983</v>
+        <v>43.041419506073</v>
       </c>
     </row>
     <row r="16">
@@ -886,28 +874,28 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>0.01683875223913889</v>
+        <v>0.01198069023084043</v>
       </c>
       <c r="C16" t="n">
         <v>0.0009524135262330098</v>
       </c>
       <c r="D16" t="n">
-        <v>0.03748247550439486</v>
+        <v>0.0255288116849114</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9897807506503159</v>
+        <v>0.9929394277220365</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9824753559693319</v>
+        <v>0.9944237918215614</v>
       </c>
       <c r="G16" t="n">
-        <v>0.997405485544848</v>
+        <v>0.991475166790215</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9898841272760713</v>
+        <v>0.9929472902746845</v>
       </c>
       <c r="I16" t="n">
-        <v>74.54774355888367</v>
+        <v>43.64671182632446</v>
       </c>
     </row>
     <row r="17">
@@ -915,28 +903,28 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>0.01154065265980894</v>
+        <v>0.01253339614027601</v>
       </c>
       <c r="C17" t="n">
         <v>0.0009455032620941839</v>
       </c>
       <c r="D17" t="n">
-        <v>0.03547986600835278</v>
+        <v>0.02757644658898233</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9895949461166852</v>
+        <v>0.9923820141211446</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9925428784489188</v>
+        <v>0.9940498326515433</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9866567828020756</v>
+        <v>0.9907338769458859</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9895910780669145</v>
+        <v>0.9923890848338592</v>
       </c>
       <c r="I17" t="n">
-        <v>73.81126523017883</v>
+        <v>43.7723081111908</v>
       </c>
     </row>
     <row r="18">
@@ -944,28 +932,28 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>0.01335266946803624</v>
+        <v>0.0120905767090966</v>
       </c>
       <c r="C18" t="n">
         <v>0.0009381533400219318</v>
       </c>
       <c r="D18" t="n">
-        <v>0.02096176634132091</v>
+        <v>0.02103880905177198</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9946116685247121</v>
+        <v>0.9940542549238202</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9977620290936218</v>
+        <v>0.9944362017804155</v>
       </c>
       <c r="G18" t="n">
-        <v>0.991475166790215</v>
+        <v>0.9936990363232023</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9946086633203197</v>
+        <v>0.9940674823878384</v>
       </c>
       <c r="I18" t="n">
-        <v>73.31152629852295</v>
+        <v>42.55563902854919</v>
       </c>
     </row>
     <row r="19">
@@ -973,28 +961,28 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>0.01356002529180106</v>
+        <v>0.007550365147003227</v>
       </c>
       <c r="C19" t="n">
         <v>0.0009303710135019719</v>
       </c>
       <c r="D19" t="n">
-        <v>0.03589470921784843</v>
+        <v>0.03407134370722573</v>
       </c>
       <c r="E19" t="n">
         <v>0.9895949461166852</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9951274362818591</v>
+        <v>0.9962434259954921</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9840622683469237</v>
+        <v>0.9829503335804299</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9895639209839732</v>
+        <v>0.9895522388059701</v>
       </c>
       <c r="I19" t="n">
-        <v>73.09491276741028</v>
+        <v>42.75757360458374</v>
       </c>
     </row>
     <row r="20">
@@ -1002,28 +990,28 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>0.01238236567923821</v>
+        <v>0.01566389177290257</v>
       </c>
       <c r="C20" t="n">
         <v>0.0009221639627510076</v>
       </c>
       <c r="D20" t="n">
-        <v>0.02669358695306149</v>
+        <v>0.01412121816068566</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9927536231884058</v>
+        <v>0.9960981047937569</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9907715023994094</v>
+        <v>0.9937292511988196</v>
       </c>
       <c r="G20" t="n">
-        <v>0.9948109710896961</v>
+        <v>0.9985174203113417</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9927871277972998</v>
+        <v>0.9961175818080976</v>
       </c>
       <c r="I20" t="n">
-        <v>73.17482876777649</v>
+        <v>42.84633231163025</v>
       </c>
     </row>
     <row r="21">
@@ -1031,28 +1019,28 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>0.0104552375868497</v>
+        <v>0.007342606253534587</v>
       </c>
       <c r="C21" t="n">
         <v>0.000913540287137281</v>
       </c>
       <c r="D21" t="n">
-        <v>0.03209397834729122</v>
+        <v>0.02419740389043602</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9899665551839465</v>
+        <v>0.9923820141211446</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9921816827997022</v>
+        <v>0.9940498326515433</v>
       </c>
       <c r="G21" t="n">
-        <v>0.9877687175685693</v>
+        <v>0.9907338769458859</v>
       </c>
       <c r="H21" t="n">
-        <v>0.9899702823179792</v>
+        <v>0.9923890848338592</v>
       </c>
       <c r="I21" t="n">
-        <v>73.19453811645508</v>
+        <v>42.40874838829041</v>
       </c>
     </row>
     <row r="22">
@@ -1060,28 +1048,28 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>0.009153933911161816</v>
+        <v>0.01062982257332183</v>
       </c>
       <c r="C22" t="n">
         <v>0.0009045084971874739</v>
       </c>
       <c r="D22" t="n">
-        <v>0.02266895311556346</v>
+        <v>0.03539871899113155</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9931252322556671</v>
+        <v>0.9908955778520996</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9962700484893696</v>
+        <v>0.9892870336165497</v>
       </c>
       <c r="G22" t="n">
-        <v>0.9899925871015567</v>
+        <v>0.9925871015567087</v>
       </c>
       <c r="H22" t="n">
-        <v>0.9931213980293735</v>
+        <v>0.9909343200740055</v>
       </c>
       <c r="I22" t="n">
-        <v>73.47127676010132</v>
+        <v>42.26622343063354</v>
       </c>
     </row>
     <row r="23">
@@ -1089,28 +1077,28 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>0.009585691437261946</v>
+        <v>0.008600158041132188</v>
       </c>
       <c r="C23" t="n">
         <v>0.0008950775061878453</v>
       </c>
       <c r="D23" t="n">
-        <v>0.03124544211885804</v>
+        <v>0.01137863034020387</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9934968413229283</v>
+        <v>0.9960981047937569</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9915097822074567</v>
+        <v>0.9944588104913188</v>
       </c>
       <c r="G23" t="n">
-        <v>0.9955522609340252</v>
+        <v>0.9977761304670126</v>
       </c>
       <c r="H23" t="n">
-        <v>0.9935269095616793</v>
+        <v>0.9961147086031452</v>
       </c>
       <c r="I23" t="n">
-        <v>73.17144680023193</v>
+        <v>42.0834276676178</v>
       </c>
     </row>
     <row r="24">
@@ -1118,28 +1106,28 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>0.01019661517745237</v>
+        <v>0.007696263726638101</v>
       </c>
       <c r="C24" t="n">
         <v>0.0008852566213878948</v>
       </c>
       <c r="D24" t="n">
-        <v>0.01896015496536354</v>
+        <v>0.02406543560805968</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9949832775919732</v>
+        <v>0.9920104050538833</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9940806511283758</v>
+        <v>0.994413407821229</v>
       </c>
       <c r="G24" t="n">
-        <v>0.9959229058561898</v>
+        <v>0.9896219421793921</v>
       </c>
       <c r="H24" t="n">
-        <v>0.99500092575449</v>
+        <v>0.99201188928107</v>
       </c>
       <c r="I24" t="n">
-        <v>73.35265970230103</v>
+        <v>42.53195738792419</v>
       </c>
     </row>
     <row r="25">
@@ -1147,28 +1135,28 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>0.004995743554084152</v>
+        <v>0.008571925220553533</v>
       </c>
       <c r="C25" t="n">
         <v>0.0008750555348152299</v>
       </c>
       <c r="D25" t="n">
-        <v>0.01059560343266166</v>
+        <v>0.02347052700404879</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9977703455964325</v>
+        <v>0.9923820141211446</v>
       </c>
       <c r="F25" t="n">
-        <v>0.997039230199852</v>
+        <v>0.9940498326515433</v>
       </c>
       <c r="G25" t="n">
-        <v>0.9985174203113417</v>
+        <v>0.9907338769458859</v>
       </c>
       <c r="H25" t="n">
-        <v>0.9977777777777778</v>
+        <v>0.9923890848338592</v>
       </c>
       <c r="I25" t="n">
-        <v>74.53079867362976</v>
+        <v>43.08227229118347</v>
       </c>
     </row>
     <row r="26">
@@ -1176,28 +1164,28 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>0.0107973917414681</v>
+        <v>0.006554622160778251</v>
       </c>
       <c r="C26" t="n">
         <v>0.0008644843137107058</v>
       </c>
       <c r="D26" t="n">
-        <v>0.03433831428785908</v>
+        <v>0.01361474469839664</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9908955778520996</v>
+        <v>0.9951690821256038</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9914656771799629</v>
+        <v>0.9951816160118606</v>
       </c>
       <c r="G26" t="n">
-        <v>0.9903632320237212</v>
+        <v>0.9951816160118606</v>
       </c>
       <c r="H26" t="n">
-        <v>0.9909141479695902</v>
+        <v>0.9951816160118606</v>
       </c>
       <c r="I26" t="n">
-        <v>73.55436134338379</v>
+        <v>43.59928822517395</v>
       </c>
     </row>
     <row r="27">
@@ -1205,28 +1193,28 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>0.01060157992099869</v>
+        <v>0.006849663925069552</v>
       </c>
       <c r="C27" t="n">
         <v>0.0008535533905932738</v>
       </c>
       <c r="D27" t="n">
-        <v>0.02343124696427265</v>
+        <v>0.0161869131497198</v>
       </c>
       <c r="E27" t="n">
-        <v>0.9933110367892977</v>
+        <v>0.9951690821256038</v>
       </c>
       <c r="F27" t="n">
-        <v>0.9904200442151806</v>
+        <v>0.9948148148148148</v>
       </c>
       <c r="G27" t="n">
-        <v>0.9962935507783544</v>
+        <v>0.9955522609340252</v>
       </c>
       <c r="H27" t="n">
-        <v>0.9933481152993349</v>
+        <v>0.9951834012597258</v>
       </c>
       <c r="I27" t="n">
-        <v>73.4979248046875</v>
+        <v>42.41871547698975</v>
       </c>
     </row>
     <row r="28">
@@ -1234,28 +1222,28 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>0.007189396531982972</v>
+        <v>0.008264145877536169</v>
       </c>
       <c r="C28" t="n">
         <v>0.0008422735529643445</v>
       </c>
       <c r="D28" t="n">
-        <v>0.02388094530748093</v>
+        <v>0.02252031867150834</v>
       </c>
       <c r="E28" t="n">
-        <v>0.9927536231884058</v>
+        <v>0.9934968413229283</v>
       </c>
       <c r="F28" t="n">
-        <v>0.9900479174345743</v>
+        <v>0.9962728289228475</v>
       </c>
       <c r="G28" t="n">
-        <v>0.9955522609340252</v>
+        <v>0.9907338769458859</v>
       </c>
       <c r="H28" t="n">
-        <v>0.9927924598041028</v>
+        <v>0.9934956327820108</v>
       </c>
       <c r="I28" t="n">
-        <v>73.21480131149292</v>
+        <v>42.18849039077759</v>
       </c>
     </row>
     <row r="29">
@@ -1263,28 +1251,28 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>0.007634348897920298</v>
+        <v>0.006610361892163122</v>
       </c>
       <c r="C29" t="n">
         <v>0.000830655932661826</v>
       </c>
       <c r="D29" t="n">
-        <v>0.01581833798418679</v>
+        <v>0.01655687593696733</v>
       </c>
       <c r="E29" t="n">
-        <v>0.9955406911928651</v>
+        <v>0.9949832775919732</v>
       </c>
       <c r="F29" t="n">
-        <v>0.9955522609340252</v>
+        <v>0.9937153419593345</v>
       </c>
       <c r="G29" t="n">
-        <v>0.9955522609340252</v>
+        <v>0.9962935507783544</v>
       </c>
       <c r="H29" t="n">
-        <v>0.9955522609340252</v>
+        <v>0.9950027762354248</v>
       </c>
       <c r="I29" t="n">
-        <v>73.07788252830505</v>
+        <v>42.6276478767395</v>
       </c>
     </row>
     <row r="30">
@@ -1292,28 +1280,28 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>0.006302503404281649</v>
+        <v>0.006468492340599048</v>
       </c>
       <c r="C30" t="n">
         <v>0.000818711994874345</v>
       </c>
       <c r="D30" t="n">
-        <v>0.02432367799630714</v>
+        <v>0.01487643917041099</v>
       </c>
       <c r="E30" t="n">
-        <v>0.9936826458565589</v>
+        <v>0.9955406911928651</v>
       </c>
       <c r="F30" t="n">
-        <v>0.9882697947214076</v>
+        <v>0.9948186528497409</v>
       </c>
       <c r="G30" t="n">
-        <v>0.9992587101556709</v>
+        <v>0.9962935507783544</v>
       </c>
       <c r="H30" t="n">
-        <v>0.9937338739402876</v>
+        <v>0.9955555555555555</v>
       </c>
       <c r="I30" t="n">
-        <v>73.12227916717529</v>
+        <v>42.12624192237854</v>
       </c>
     </row>
     <row r="31">
@@ -1321,28 +1309,28 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>0.005496364756497732</v>
+        <v>0.007420750120115438</v>
       </c>
       <c r="C31" t="n">
         <v>0.0008064535268264884</v>
       </c>
       <c r="D31" t="n">
-        <v>0.01047643686805062</v>
+        <v>0.01469909050865681</v>
       </c>
       <c r="E31" t="n">
-        <v>0.9968413229282794</v>
+        <v>0.9951690821256038</v>
       </c>
       <c r="F31" t="n">
-        <v>0.9966654316413487</v>
+        <v>0.9911764705882353</v>
       </c>
       <c r="G31" t="n">
-        <v>0.9970348406226834</v>
+        <v>0.9992587101556709</v>
       </c>
       <c r="H31" t="n">
-        <v>0.9968501019084677</v>
+        <v>0.9952011812476929</v>
       </c>
       <c r="I31" t="n">
-        <v>72.81916856765747</v>
+        <v>42.56609296798706</v>
       </c>
     </row>
     <row r="32">
@@ -1350,28 +1338,28 @@
         <v>31</v>
       </c>
       <c r="B32" t="n">
-        <v>0.003487635744449598</v>
+        <v>0.004751872608942175</v>
       </c>
       <c r="C32" t="n">
         <v>0.0007938926261462368</v>
       </c>
       <c r="D32" t="n">
-        <v>0.01805767418064808</v>
+        <v>0.01606536572963979</v>
       </c>
       <c r="E32" t="n">
-        <v>0.9960981047937569</v>
+        <v>0.9946116685247121</v>
       </c>
       <c r="F32" t="n">
-        <v>0.9959244164505372</v>
+        <v>0.9944423860689144</v>
       </c>
       <c r="G32" t="n">
-        <v>0.9962935507783544</v>
+        <v>0.9948109710896961</v>
       </c>
       <c r="H32" t="n">
-        <v>0.9961089494163424</v>
+        <v>0.9946266444320919</v>
       </c>
       <c r="I32" t="n">
-        <v>72.4548933506012</v>
+        <v>42.56312251091003</v>
       </c>
     </row>
     <row r="33">
@@ -1379,28 +1367,28 @@
         <v>32</v>
       </c>
       <c r="B33" t="n">
-        <v>0.00717492068103718</v>
+        <v>0.005463001667801635</v>
       </c>
       <c r="C33" t="n">
         <v>0.0007810416889260655</v>
       </c>
       <c r="D33" t="n">
-        <v>0.02096619777691057</v>
+        <v>0.01362757605261726</v>
       </c>
       <c r="E33" t="n">
-        <v>0.9942400594574508</v>
+        <v>0.9959123002601263</v>
       </c>
       <c r="F33" t="n">
-        <v>0.9926117473217584</v>
+        <v>0.9951887490747594</v>
       </c>
       <c r="G33" t="n">
-        <v>0.9959229058561898</v>
+        <v>0.9966641957005189</v>
       </c>
       <c r="H33" t="n">
-        <v>0.9942645698427383</v>
+        <v>0.9959259259259259</v>
       </c>
       <c r="I33" t="n">
-        <v>72.43797087669373</v>
+        <v>42.41805744171143</v>
       </c>
     </row>
     <row r="34">
@@ -1408,28 +1396,28 @@
         <v>33</v>
       </c>
       <c r="B34" t="n">
-        <v>0.004681239058158082</v>
+        <v>0.002927966811106885</v>
       </c>
       <c r="C34" t="n">
         <v>0.0007679133974894984</v>
       </c>
       <c r="D34" t="n">
-        <v>0.02451651187106614</v>
+        <v>0.01542018429172196</v>
       </c>
       <c r="E34" t="n">
-        <v>0.9925678186547752</v>
+        <v>0.9957264957264957</v>
       </c>
       <c r="F34" t="n">
-        <v>0.986100950987564</v>
+        <v>0.9959213941416388</v>
       </c>
       <c r="G34" t="n">
-        <v>0.9992587101556709</v>
+        <v>0.9955522609340252</v>
       </c>
       <c r="H34" t="n">
-        <v>0.9926362297496318</v>
+        <v>0.9957367933271548</v>
       </c>
       <c r="I34" t="n">
-        <v>72.71189284324646</v>
+        <v>42.15520620346069</v>
       </c>
     </row>
     <row r="35">
@@ -1437,28 +1425,28 @@
         <v>34</v>
       </c>
       <c r="B35" t="n">
-        <v>0.002767432137116894</v>
+        <v>0.009948164505215237</v>
       </c>
       <c r="C35" t="n">
         <v>0.0007545207078751858</v>
       </c>
       <c r="D35" t="n">
-        <v>0.009281524906935954</v>
+        <v>0.0139250073404082</v>
       </c>
       <c r="E35" t="n">
-        <v>0.9973987365291713</v>
+        <v>0.9949832775919732</v>
       </c>
       <c r="F35" t="n">
-        <v>0.9966691339748335</v>
+        <v>0.9981350242446848</v>
       </c>
       <c r="G35" t="n">
-        <v>0.9981467753891772</v>
+        <v>0.9918458117123795</v>
       </c>
       <c r="H35" t="n">
-        <v>0.9974074074074074</v>
+        <v>0.9949804796430564</v>
       </c>
       <c r="I35" t="n">
-        <v>73.74791407585144</v>
+        <v>42.16823172569275</v>
       </c>
     </row>
     <row r="36">
@@ -1466,28 +1454,28 @@
         <v>35</v>
       </c>
       <c r="B36" t="n">
-        <v>0.004500767883639957</v>
+        <v>0.003128986327399422</v>
       </c>
       <c r="C36" t="n">
         <v>0.0007408768370508578</v>
       </c>
       <c r="D36" t="n">
-        <v>0.02966721499763765</v>
+        <v>0.01342038162800144</v>
       </c>
       <c r="E36" t="n">
-        <v>0.9905239687848384</v>
+        <v>0.9966555183946488</v>
       </c>
       <c r="F36" t="n">
-        <v>0.9892791127541589</v>
+        <v>0.9948301329394387</v>
       </c>
       <c r="G36" t="n">
-        <v>0.9918458117123795</v>
+        <v>0.9985174203113417</v>
       </c>
       <c r="H36" t="n">
-        <v>0.9905607995558023</v>
+        <v>0.9966703662597114</v>
       </c>
       <c r="I36" t="n">
-        <v>73.71131348609924</v>
+        <v>42.65588545799255</v>
       </c>
     </row>
     <row r="37">
@@ -1495,28 +1483,28 @@
         <v>36</v>
       </c>
       <c r="B37" t="n">
-        <v>0.006552890790107035</v>
+        <v>0.00334321270263475</v>
       </c>
       <c r="C37" t="n">
         <v>0.0007269952498697736</v>
       </c>
       <c r="D37" t="n">
-        <v>0.01238141851355234</v>
+        <v>0.009251553298929795</v>
       </c>
       <c r="E37" t="n">
-        <v>0.9964697138610182</v>
+        <v>0.9975845410628019</v>
       </c>
       <c r="F37" t="n">
-        <v>0.9962949240459429</v>
+        <v>0.999256229081443</v>
       </c>
       <c r="G37" t="n">
-        <v>0.9966641957005189</v>
+        <v>0.9959229058561898</v>
       </c>
       <c r="H37" t="n">
-        <v>0.9964795256624051</v>
+        <v>0.9975867829961017</v>
       </c>
       <c r="I37" t="n">
-        <v>73.57126021385193</v>
+        <v>42.25767993927002</v>
       </c>
     </row>
     <row r="38">
@@ -1524,28 +1512,28 @@
         <v>37</v>
       </c>
       <c r="B38" t="n">
-        <v>0.007240278794385373</v>
+        <v>0.001252725630887245</v>
       </c>
       <c r="C38" t="n">
         <v>0.0007128896457825365</v>
       </c>
       <c r="D38" t="n">
-        <v>0.02428235189497372</v>
+        <v>0.01210182166064657</v>
       </c>
       <c r="E38" t="n">
-        <v>0.9920104050538833</v>
+        <v>0.9962839093273876</v>
       </c>
       <c r="F38" t="n">
-        <v>0.9885903570114096</v>
+        <v>0.9962935507783544</v>
       </c>
       <c r="G38" t="n">
-        <v>0.9955522609340252</v>
+        <v>0.9962935507783544</v>
       </c>
       <c r="H38" t="n">
-        <v>0.9920590951061865</v>
+        <v>0.9962935507783544</v>
       </c>
       <c r="I38" t="n">
-        <v>73.49794721603394</v>
+        <v>43.39398193359375</v>
       </c>
     </row>
     <row r="39">
@@ -1553,28 +1541,28 @@
         <v>38</v>
       </c>
       <c r="B39" t="n">
-        <v>0.002379567073838008</v>
+        <v>0.006394682510679161</v>
       </c>
       <c r="C39" t="n">
         <v>0.0006985739453173904</v>
       </c>
       <c r="D39" t="n">
-        <v>0.01571032291250431</v>
+        <v>0.0309874714846891</v>
       </c>
       <c r="E39" t="n">
-        <v>0.99702712746191</v>
+        <v>0.9912671869193609</v>
       </c>
       <c r="F39" t="n">
-        <v>0.996299037749815</v>
+        <v>0.9874954027215889</v>
       </c>
       <c r="G39" t="n">
-        <v>0.9977761304670126</v>
+        <v>0.9951816160118606</v>
       </c>
       <c r="H39" t="n">
-        <v>0.9970370370370371</v>
+        <v>0.9913236108547167</v>
       </c>
       <c r="I39" t="n">
-        <v>73.38988351821899</v>
+        <v>43.13500738143921</v>
       </c>
     </row>
     <row r="40">
@@ -1582,28 +1570,28 @@
         <v>39</v>
       </c>
       <c r="B40" t="n">
-        <v>0.0002072316215155816</v>
+        <v>0.003836067310091195</v>
       </c>
       <c r="C40" t="n">
         <v>0.0006840622763423392</v>
       </c>
       <c r="D40" t="n">
-        <v>0.01522908999247607</v>
+        <v>0.02010983448995378</v>
       </c>
       <c r="E40" t="n">
-        <v>0.9957264957264957</v>
+        <v>0.9933110367892977</v>
       </c>
       <c r="F40" t="n">
-        <v>0.9977670264235207</v>
+        <v>0.9929629629629629</v>
       </c>
       <c r="G40" t="n">
         <v>0.9936990363232023</v>
       </c>
       <c r="H40" t="n">
-        <v>0.9957288765088208</v>
+        <v>0.9933308632826973</v>
       </c>
       <c r="I40" t="n">
-        <v>73.0341911315918</v>
+        <v>42.50614595413208</v>
       </c>
     </row>
     <row r="41">
@@ -1611,28 +1599,28 @@
         <v>40</v>
       </c>
       <c r="B41" t="n">
-        <v>4.405189756072168e-05</v>
+        <v>0.001168088534521716</v>
       </c>
       <c r="C41" t="n">
         <v>0.0006693689601226459</v>
       </c>
       <c r="D41" t="n">
-        <v>0.0134144366396324</v>
+        <v>0.01326913173687201</v>
       </c>
       <c r="E41" t="n">
         <v>0.9968413229282794</v>
       </c>
       <c r="F41" t="n">
-        <v>0.9970337411939192</v>
+        <v>0.9966654316413487</v>
       </c>
       <c r="G41" t="n">
-        <v>0.9966641957005189</v>
+        <v>0.9970348406226834</v>
       </c>
       <c r="H41" t="n">
-        <v>0.9968489341983318</v>
+        <v>0.9968501019084677</v>
       </c>
       <c r="I41" t="n">
-        <v>73.15460157394409</v>
+        <v>42.26708960533142</v>
       </c>
     </row>
     <row r="42">
@@ -1640,28 +1628,28 @@
         <v>41</v>
       </c>
       <c r="B42" t="n">
-        <v>0.006371530613855888</v>
+        <v>7.673951550537061e-05</v>
       </c>
       <c r="C42" t="n">
         <v>0.0006545084971874739</v>
       </c>
       <c r="D42" t="n">
-        <v>0.02189878495842337</v>
+        <v>0.01788220981722471</v>
       </c>
       <c r="E42" t="n">
-        <v>0.9925678186547752</v>
+        <v>0.9964697138610182</v>
       </c>
       <c r="F42" t="n">
-        <v>0.9914940828402367</v>
+        <v>0.9977703455964325</v>
       </c>
       <c r="G42" t="n">
-        <v>0.9936990363232023</v>
+        <v>0.9951816160118606</v>
       </c>
       <c r="H42" t="n">
-        <v>0.9925953350610884</v>
+        <v>0.9964742994989794</v>
       </c>
       <c r="I42" t="n">
-        <v>72.67114067077637</v>
+        <v>42.4419093132019</v>
       </c>
     </row>
     <row r="43">
@@ -1669,28 +1657,28 @@
         <v>42</v>
       </c>
       <c r="B43" t="n">
-        <v>0.00693475682682629</v>
+        <v>0.004457473989479023</v>
       </c>
       <c r="C43" t="n">
         <v>0.0006394955530196148</v>
       </c>
       <c r="D43" t="n">
-        <v>0.01934725588970107</v>
+        <v>0.02358780741866944</v>
       </c>
       <c r="E43" t="n">
-        <v>0.9931252322556671</v>
+        <v>0.9929394277220365</v>
       </c>
       <c r="F43" t="n">
-        <v>0.9955307262569832</v>
+        <v>0.9922279792746114</v>
       </c>
       <c r="G43" t="n">
-        <v>0.9907338769458859</v>
+        <v>0.9936990363232023</v>
       </c>
       <c r="H43" t="n">
-        <v>0.9931265093813858</v>
+        <v>0.9929629629629629</v>
       </c>
       <c r="I43" t="n">
-        <v>72.49813389778137</v>
+        <v>42.38698959350586</v>
       </c>
     </row>
     <row r="44">
@@ -1698,28 +1686,28 @@
         <v>43</v>
       </c>
       <c r="B44" t="n">
-        <v>0.004090587454175101</v>
+        <v>0.005386291628859027</v>
       </c>
       <c r="C44" t="n">
         <v>0.0006243449435824275</v>
       </c>
       <c r="D44" t="n">
-        <v>0.01918431138055786</v>
+        <v>0.0131095796118993</v>
       </c>
       <c r="E44" t="n">
-        <v>0.9942400594574508</v>
+        <v>0.9951690821256038</v>
       </c>
       <c r="F44" t="n">
-        <v>0.9940718784735088</v>
+        <v>0.9929889298892989</v>
       </c>
       <c r="G44" t="n">
-        <v>0.9944403261675315</v>
+        <v>0.997405485544848</v>
       </c>
       <c r="H44" t="n">
-        <v>0.9942560681860293</v>
+        <v>0.9951923076923077</v>
       </c>
       <c r="I44" t="n">
-        <v>72.19489407539368</v>
+        <v>42.1918888092041</v>
       </c>
     </row>
     <row r="45">
@@ -1727,28 +1715,28 @@
         <v>44</v>
       </c>
       <c r="B45" t="n">
-        <v>0.005458022848925722</v>
+        <v>0.001368726800324835</v>
       </c>
       <c r="C45" t="n">
         <v>0.0006090716206982715</v>
       </c>
       <c r="D45" t="n">
-        <v>0.02611072336085218</v>
+        <v>0.0118961054166951</v>
       </c>
       <c r="E45" t="n">
-        <v>0.9931252322556671</v>
+        <v>0.9957264957264957</v>
       </c>
       <c r="F45" t="n">
-        <v>0.9882568807339449</v>
+        <v>0.998509131569139</v>
       </c>
       <c r="G45" t="n">
-        <v>0.9981467753891772</v>
+        <v>0.9929577464788732</v>
       </c>
       <c r="H45" t="n">
-        <v>0.9931772081873502</v>
+        <v>0.9957257015424642</v>
       </c>
       <c r="I45" t="n">
-        <v>72.14581322669983</v>
+        <v>42.4463586807251</v>
       </c>
     </row>
     <row r="46">
@@ -1756,28 +1744,28 @@
         <v>45</v>
       </c>
       <c r="B46" t="n">
-        <v>0.0007601770031427153</v>
+        <v>0.002605740099966676</v>
       </c>
       <c r="C46" t="n">
         <v>0.0005936906572928626</v>
       </c>
       <c r="D46" t="n">
-        <v>0.01282606610819657</v>
+        <v>0.05217216655016149</v>
       </c>
       <c r="E46" t="n">
-        <v>0.9964697138610182</v>
+        <v>0.9864362690449647</v>
       </c>
       <c r="F46" t="n">
-        <v>0.9948282231252309</v>
+        <v>0.9802414928649835</v>
       </c>
       <c r="G46" t="n">
-        <v>0.9981467753891772</v>
+        <v>0.9929577464788732</v>
       </c>
       <c r="H46" t="n">
-        <v>0.9964847363552266</v>
+        <v>0.9865586448167925</v>
       </c>
       <c r="I46" t="n">
-        <v>72.38791847229004</v>
+        <v>42.49272799491882</v>
       </c>
     </row>
     <row r="47">
@@ -1785,28 +1773,28 @@
         <v>46</v>
       </c>
       <c r="B47" t="n">
-        <v>0.001572050512789248</v>
+        <v>0.004462753014826292</v>
       </c>
       <c r="C47" t="n">
         <v>0.0005782172325201157</v>
       </c>
       <c r="D47" t="n">
-        <v>0.02395719393085345</v>
+        <v>0.02743188007714696</v>
       </c>
       <c r="E47" t="n">
-        <v>0.9938684503901896</v>
+        <v>0.9934968413229283</v>
       </c>
       <c r="F47" t="n">
-        <v>0.9893499816378993</v>
+        <v>0.9970138111235536</v>
       </c>
       <c r="G47" t="n">
-        <v>0.9985174203113417</v>
+        <v>0.9899925871015567</v>
       </c>
       <c r="H47" t="n">
-        <v>0.993912562257886</v>
+        <v>0.993490794123117</v>
       </c>
       <c r="I47" t="n">
-        <v>73.48146820068359</v>
+        <v>43.17077326774597</v>
       </c>
     </row>
     <row r="48">
@@ -1814,28 +1802,28 @@
         <v>47</v>
       </c>
       <c r="B48" t="n">
-        <v>0.002167919531801692</v>
+        <v>0.001536009943463845</v>
       </c>
       <c r="C48" t="n">
         <v>0.0005626666167821524</v>
       </c>
       <c r="D48" t="n">
-        <v>0.01896593204049722</v>
+        <v>0.01673406962673941</v>
       </c>
       <c r="E48" t="n">
-        <v>0.9953548866592344</v>
+        <v>0.9960981047937569</v>
       </c>
       <c r="F48" t="n">
-        <v>0.994816734542762</v>
+        <v>0.9988818486768543</v>
       </c>
       <c r="G48" t="n">
-        <v>0.9959229058561898</v>
+        <v>0.9933283914010378</v>
       </c>
       <c r="H48" t="n">
-        <v>0.9953695128727542</v>
+        <v>0.9960973796692064</v>
       </c>
       <c r="I48" t="n">
-        <v>73.13827443122864</v>
+        <v>42.61432957649231</v>
       </c>
     </row>
     <row r="49">
@@ -1843,28 +1831,28 @@
         <v>48</v>
       </c>
       <c r="B49" t="n">
-        <v>0.0001003616458323528</v>
+        <v>0.0006555290582206502</v>
       </c>
       <c r="C49" t="n">
         <v>0.0005470541566592573</v>
       </c>
       <c r="D49" t="n">
-        <v>0.02068208173076011</v>
+        <v>0.01713850714109146</v>
       </c>
       <c r="E49" t="n">
-        <v>0.9957264957264957</v>
+        <v>0.9955406911928651</v>
       </c>
       <c r="F49" t="n">
-        <v>0.9951869677897075</v>
+        <v>0.9951851851851852</v>
       </c>
       <c r="G49" t="n">
-        <v>0.9962935507783544</v>
+        <v>0.9959229058561898</v>
       </c>
       <c r="H49" t="n">
-        <v>0.9957399518429338</v>
+        <v>0.9955539088551315</v>
       </c>
       <c r="I49" t="n">
-        <v>73.2811005115509</v>
+        <v>43.18179273605347</v>
       </c>
     </row>
     <row r="50">
@@ -1872,28 +1860,28 @@
         <v>49</v>
       </c>
       <c r="B50" t="n">
-        <v>0.005723135290493959</v>
+        <v>0.001643048560982001</v>
       </c>
       <c r="C50" t="n">
         <v>0.000531395259764657</v>
       </c>
       <c r="D50" t="n">
-        <v>0.01654811114650657</v>
+        <v>0.01442745958810164</v>
       </c>
       <c r="E50" t="n">
-        <v>0.9955406911928651</v>
+        <v>0.9953548866592344</v>
       </c>
       <c r="F50" t="n">
-        <v>0.9933579335793358</v>
+        <v>0.9944506104328524</v>
       </c>
       <c r="G50" t="n">
-        <v>0.9977761304670126</v>
+        <v>0.9962935507783544</v>
       </c>
       <c r="H50" t="n">
-        <v>0.9955621301775148</v>
+        <v>0.9953712275504536</v>
       </c>
       <c r="I50" t="n">
-        <v>73.2550311088562</v>
+        <v>43.54098176956177</v>
       </c>
     </row>
     <row r="51">
@@ -1901,28 +1889,28 @@
         <v>50</v>
       </c>
       <c r="B51" t="n">
-        <v>0.001172958484682417</v>
+        <v>0.003193447473604756</v>
       </c>
       <c r="C51" t="n">
         <v>0.0005157053795390644</v>
       </c>
       <c r="D51" t="n">
-        <v>0.01490853465996832</v>
+        <v>0.01292341285995554</v>
       </c>
       <c r="E51" t="n">
-        <v>0.9960981047937569</v>
+        <v>0.9962839093273876</v>
       </c>
       <c r="F51" t="n">
-        <v>0.9951905290418054</v>
+        <v>0.9955588452997779</v>
       </c>
       <c r="G51" t="n">
         <v>0.9970348406226834</v>
       </c>
       <c r="H51" t="n">
-        <v>0.996111831142381</v>
+        <v>0.9962962962962963</v>
       </c>
       <c r="I51" t="n">
-        <v>73.13654375076294</v>
+        <v>42.56692838668823</v>
       </c>
     </row>
   </sheetData>
